--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46179.5625</v>
+        <v>46179.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46179.58333333334</v>
+        <v>46179.5625</v>
       </c>
     </row>
     <row r="14">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,43 +2951,43 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.7</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>5.29</v>
+        <v>3.31</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P18" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>3.91</v>
+        <v>5.29</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.62</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P17" t="n">
-        <v>3.31</v>
+        <v>5.29</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>5.29</v>
+        <v>3.31</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,43 +2792,43 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.7</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>5.29</v>
+        <v>3.31</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O19" t="n">
         <v>2.62</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P19" t="n">
-        <v>3.31</v>
+        <v>5.29</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,43 +2951,43 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.7</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="O22" t="n">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="P22" t="n">
-        <v>4.14</v>
+        <v>6.94</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46179.75</v>
+        <v>46179.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46179.76041666666</v>
+        <v>46179.75</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46179.83333333334</v>
+        <v>46179.76041666666</v>
       </c>
     </row>
     <row r="25">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46179.85416666666</v>
+        <v>46179.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46179.89583333334</v>
+        <v>46179.85416666666</v>
       </c>
     </row>
     <row r="28">
@@ -4962,6 +4962,165 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
+        <v>46179.89583333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
         <v>46179.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O18" t="n">
         <v>2.62</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P18" t="n">
-        <v>3.31</v>
+        <v>5.29</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="P19" t="n">
-        <v>5.29</v>
+        <v>3.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>5.29</v>
+        <v>3.31</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.47</v>
+        <v>3.58</v>
       </c>
       <c r="P19" t="n">
-        <v>3.91</v>
+        <v>6.94</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,16 +3461,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46179.64583333334</v>
+        <v>46179.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46179.66666666666</v>
+        <v>46179.75</v>
       </c>
     </row>
     <row r="23">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46179.75</v>
+        <v>46179.76041666666</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46179.76041666666</v>
+        <v>46179.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46179.83333333334</v>
+        <v>46179.85416666666</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46179.85416666666</v>
+        <v>46179.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4962,165 +4962,6 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>46179.89583333334</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="3" t="n">
         <v>46179.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P18" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>6.94</v>
+        <v>3.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P20" t="n">
-        <v>3.7</v>
+        <v>6.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,43 +2792,43 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.7</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P19" t="n">
-        <v>3.7</v>
+        <v>6.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>6.94</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2165,28 +2165,28 @@
         <v>3.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
         <v>1.58</v>
@@ -2195,25 +2195,25 @@
         <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,43 +2951,43 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.7</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P20" t="n">
-        <v>3.7</v>
+        <v>6.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
@@ -2189,10 +2189,10 @@
         <v>1.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>2.87</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>4.46</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
-        <v>3.91</v>
+        <v>5.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,16 +3302,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46179.66666666666</v>
+        <v>46179.64583333334</v>
       </c>
     </row>
     <row r="20">
@@ -3596,55 +3596,55 @@
         <v>6.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46179.75</v>
+        <v>46179.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46179.76041666666</v>
+        <v>46179.75</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46179.83333333334</v>
+        <v>46179.76041666666</v>
       </c>
     </row>
     <row r="25">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46179.85416666666</v>
+        <v>46179.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46179.89583333334</v>
+        <v>46179.85416666666</v>
       </c>
     </row>
     <row r="28">
@@ -4962,6 +4962,165 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
+        <v>46179.89583333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
         <v>46179.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.6</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.95</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U16" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>3.4</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA19" t="n">
         <v>3.4</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
-        <v>3.7</v>
+        <v>6.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.38</v>
       </c>
-      <c r="S21" t="n">
+      <c r="AG21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.28</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>5.29</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>5.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
         <v>2.21</v>
@@ -4262,10 +4262,10 @@
         <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC24" t="n">
         <v>2.17</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
@@ -1565,19 +1565,19 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.95</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U15" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.61</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>3.25</v>
+        <v>5.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>5.29</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4742,7 +4742,7 @@
         <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AC27" t="n">
         <v>2.12</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P4" t="n">
         <v>6</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
@@ -1565,19 +1565,19 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,43 +1679,43 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>2</v>
@@ -1724,19 +1724,19 @@
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O15" t="n">
         <v>2.6</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P16" t="n">
         <v>5.25</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>5.29</v>
+        <v>3.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,43 +3428,43 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AA19" t="n">
         <v>3.4</v>
@@ -3473,19 +3473,19 @@
         <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q20" t="n">
         <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
         <v>1.28</v>
@@ -3608,13 +3608,13 @@
         <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
@@ -3623,28 +3623,28 @@
         <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4073,55 +4073,55 @@
         <v>4.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
@@ -1565,19 +1565,19 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,43 +1679,43 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
         <v>2</v>
@@ -1724,19 +1724,19 @@
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
         <v>2.3</v>
@@ -3431,7 +3431,7 @@
         <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
         <v>4</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
@@ -1565,19 +1565,19 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,43 +1679,43 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>2</v>
@@ -1724,19 +1724,19 @@
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,43 +3269,43 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="P18" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA18" t="n">
         <v>3.4</v>
@@ -3314,19 +3314,19 @@
         <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,43 +3428,43 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.99</v>
       </c>
       <c r="AA19" t="n">
         <v>3.4</v>
@@ -3473,19 +3473,19 @@
         <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="O28" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P29" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P4" t="n">
         <v>6</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
         <v>3.58</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
         <v>4.42</v>
@@ -1559,10 +1559,10 @@
         <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>3.25</v>
@@ -2003,7 +2003,7 @@
         <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
         <v>2.8</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.19</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.6</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.95</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U16" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,43 +3269,43 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.99</v>
       </c>
       <c r="AA18" t="n">
         <v>3.4</v>
@@ -3314,19 +3314,19 @@
         <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>3.4</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.6</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.28</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.95</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U15" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.94</v>
+        <v>3.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.25</v>
       </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.6</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.28</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P26" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P28" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="O29" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.01</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>3.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>3.4</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.05</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.6</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.95</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U16" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.05</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>3.4</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P26" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
         <v>6</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,43 +1679,43 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>1.95</v>
@@ -1724,19 +1724,19 @@
         <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P15" t="n">
         <v>5.75</v>
@@ -2954,10 +2954,10 @@
         <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -3116,7 +3116,7 @@
         <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="O18" t="n">
-        <v>2.95</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P25" t="n">
-        <v>4.17</v>
+        <v>4.44</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4862,10 +4862,10 @@
         <v>2.33</v>
       </c>
       <c r="O28" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P29" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2109,27 +2109,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46179.54166666666</v>
+        <v>46179.5625</v>
       </c>
     </row>
     <row r="12">
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46179.5625</v>
+        <v>46179.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.95</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U15" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46179.625</v>
+        <v>46179.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46179.64583333334</v>
+        <v>46179.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>6.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.55</v>
+        <v>5.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46179.64583333334</v>
+        <v>46179.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,65 +3746,65 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.48</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46179.66666666666</v>
+        <v>46179.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46179.66666666666</v>
+        <v>46179.76041666666</v>
       </c>
     </row>
     <row r="23">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,81 +4064,81 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.92</v>
+        <v>3.24</v>
       </c>
       <c r="P23" t="n">
-        <v>4.14</v>
+        <v>5.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="S23" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="T23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK23" t="n">
         <v>2.05</v>
       </c>
-      <c r="U23" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46179.75</v>
+        <v>46179.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>4.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46179.76041666666</v>
+        <v>46179.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="P26" t="n">
-        <v>4.13</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46179.83333333334</v>
+        <v>46179.85416666666</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46179.85416666666</v>
+        <v>46179.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4962,165 +4962,6 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>46179.89583333334</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="3" t="n">
         <v>46179.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="O19" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P19" t="n">
-        <v>6.94</v>
+        <v>3.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.2</v>
       </c>
-      <c r="U19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="AC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.25</v>
       </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="P24" t="n">
-        <v>4.13</v>
+        <v>4.44</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>4.44</v>
+        <v>4.13</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="O18" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P18" t="n">
-        <v>6.94</v>
+        <v>3.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.2</v>
       </c>
-      <c r="U18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="AC18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.25</v>
       </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="O2" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
         <v>4.3</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="P6" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>4.42</v>
@@ -1559,7 +1559,7 @@
         <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
         <v>1.85</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
         <v>3.18</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="P9" t="n">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
         <v>4.27</v>
@@ -2513,10 +2513,10 @@
         <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>5.3</v>
@@ -2957,7 +2957,7 @@
         <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="P20" t="n">
-        <v>6.94</v>
+        <v>3.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.25</v>
       </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
         <v>3.3</v>
@@ -4067,10 +4067,10 @@
         <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q23" t="n">
         <v>2.3</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>4.44</v>
+        <v>4.73</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="P25" t="n">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="P27" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.83</v>
+        <v>3.81</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
         <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
         <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P24" t="n">
-        <v>4.73</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O25" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>3.41</v>
+        <v>4.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.28</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3.16</v>
+        <v>3.81</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="P28" t="n">
-        <v>3.81</v>
+        <v>3.16</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.41</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.28</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P25" t="n">
-        <v>4.73</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="P27" t="n">
-        <v>3.81</v>
+        <v>3.16</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>3.16</v>
+        <v>3.81</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
         <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.25</v>
       </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>3.41</v>
+        <v>4.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.28</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P24" t="n">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>1.71</v>
       </c>
       <c r="O25" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>4.97</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>3.81</v>
+        <v>4.4</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.73</v>
+        <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,49 +2156,49 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>4.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q19" t="n">
         <v>2.51</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q21" t="n">
         <v>3.3</v>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
         <v>5.5</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,49 +2315,49 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.6</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
         <v>6</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
         <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,49 +2156,49 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.6</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.67</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.28</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.61</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="P19" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.61</v>
+        <v>1.79</v>
       </c>
       <c r="O20" t="n">
-        <v>4.26</v>
+        <v>3.67</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>3.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.19</v>
+        <v>3.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>3.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.61</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="O24" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>4.6</v>
+        <v>4.97</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P25" t="n">
-        <v>4.97</v>
+        <v>4.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.61</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>1.74</v>
       </c>
       <c r="O6" t="n">
-        <v>3.76</v>
+        <v>3.17</v>
       </c>
       <c r="P6" t="n">
-        <v>3.83</v>
+        <v>3.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.67</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="P9" t="n">
-        <v>4.45</v>
+        <v>5.35</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.06</v>
+        <v>5.29</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
         <v>2.8</v>
@@ -2636,10 +2636,10 @@
         <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>2.51</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="Q21" t="n">
         <v>3.3</v>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P23" t="n">
         <v>5.5</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="O24" t="n">
         <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>4.97</v>
+        <v>4.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="P14" t="n">
-        <v>4.85</v>
+        <v>4.15</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.61</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>3.61</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>4.26</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>4.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O14" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>4.15</v>
+        <v>3.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>3.61</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>4.26</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.61</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>3.81</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P28" t="n">
-        <v>3.81</v>
+        <v>3.1</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O9" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="P9" t="n">
-        <v>5.35</v>
+        <v>4.45</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.61</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>3.61</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>4.26</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -731,7 +731,7 @@
         <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>2.39</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.53</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>4.42</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="O9" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.51</v>
+        <v>4.27</v>
       </c>
       <c r="Q14" t="n">
         <v>2.8</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
@@ -2831,10 +2831,10 @@
         <v>1.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
         <v>6.4</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
         <v>2.51</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.61</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.79</v>
+        <v>3.61</v>
       </c>
       <c r="O20" t="n">
-        <v>3.67</v>
+        <v>4.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.41</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q21" t="n">
         <v>3.3</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="Q23" t="n">
         <v>2.3</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
         <v>4.8</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
         <v>3.3</v>
       </c>
       <c r="P28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -705,23 +705,23 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '66']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46179.08333333334</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>5.26</v>
+        <v>7.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="P13" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.61</v>
+        <v>1.77</v>
       </c>
       <c r="O20" t="n">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,49 +4700,49 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.75</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '57']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46179.16666666666</v>
@@ -1049,7 +1049,7 @@
         <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="P6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="P14" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>3.4</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.65</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
         <v>3.4</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,49 +4859,49 @@
         </is>
       </c>
       <c r="N28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.75</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1020,26 +1020,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['21', '72']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46179.20833333334</v>
@@ -1179,26 +1179,26 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '80']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46179.22916666666</v>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46179.26041666666</v>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1509,21 +1509,21 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
         <v>2.53</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '61']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83', '85']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46179.3125</v>
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1671,21 +1671,21 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
         <v>4.42</v>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67', '90+9']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46179.3125</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>3.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.61</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.6</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.28</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,49 +4700,49 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.75</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.61</v>
+        <v>1.79</v>
       </c>
       <c r="O18" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q19" t="n">
         <v>2.32</v>
@@ -3470,7 +3470,7 @@
         <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
         <v>2.5</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.79</v>
+        <v>3.61</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="P20" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O25" t="n">
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
@@ -4862,10 +4862,10 @@
         <v>1.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1899,14 +1899,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
@@ -1917,28 +1917,28 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46179.45833333334</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O14" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
@@ -2954,10 +2954,10 @@
         <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>2.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>3.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.28</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>4.26</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
         <v>3.3</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P23" t="n">
-        <v>5.95</v>
+        <v>3.62</v>
       </c>
       <c r="Q23" t="n">
         <v>2.3</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1986,14 +1986,14 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46179.54166666666</v>
@@ -2124,19 +2124,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2145,24 +2145,24 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46179.5625</v>
@@ -2283,22 +2283,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2311,17 +2311,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2376,14 +2376,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46179.5625</v>
@@ -2432,26 +2432,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2463,118 +2463,118 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>4.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>['47', '57', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46179.58333333334</v>
@@ -2591,149 +2591,149 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>4.83</v>
+        <v>4.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '78']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '27']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46179.58333333334</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2871,28 +2871,28 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46179.625</v>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '38']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46179.64583333334</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3189,28 +3189,28 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46179.64583333334</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.61</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,32 +3386,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3420,115 +3420,115 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.25</v>
       </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46179.66666666666</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3583,68 +3583,68 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>4.26</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O23" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="Q23" t="n">
         <v>2.3</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="O24" t="n">
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>4.33</v>
+        <v>6.2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>6.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-06.xlsx
+++ b/jogos_2026-06-06.xlsx
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ11" t="n">
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.23</v>
+        <v>1.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.83</v>
+        <v>1.57</v>
       </c>
       <c r="AS11" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="AT11" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46179.5625</v>
@@ -2283,31 +2283,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN12" t="n">
         <v>3</v>
       </c>
-      <c r="AN12" t="n">
-        <v>2</v>
-      </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.15</v>
+        <v>3.23</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="AT12" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46179.5625</v>
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3825,28 +3825,28 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO21" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP21" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46179.6875</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
